--- a/docs/page-copy/03-创始人故事.xlsx
+++ b/docs/page-copy/03-创始人故事.xlsx
@@ -529,7 +529,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D6" t="str">
-        <v>I, John LONG WOO, and my two sons Caros Woo and Sam, the three of us, have too many legendary stories with the spiritual realm. These experiences make us the first door opener in the spiritual realm and the first explorer of the truth of spirit life.</v>
+        <v>I, John LONG WOO, and my two sons Caros Woo and Sam, the three of us, have too many legendary stories with the spiritual realm. These experiences make us the first door opener in the spiritual realm and the first explorer of the truth of **spirit (soul)** life.</v>
       </c>
       <c r="E6" t="str">
         <v>我， John LONG WOO, 和我的两个儿子Caros Woo和Sam，我们父子三人，与灵魂世界有太多传奇的故事。这些经历造就我们是灵魂世界首位开门者，并且是灵魂生命真相的首位探索者。</v>
@@ -598,7 +598,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D9" t="str">
-        <v>A living person is composed of both the physical body and the spirit (soul). After death, the spirit becomes a ghost (spirit ghost). But for the billions of ghosts, the only means of survival is to obtain energy by attaching to human beings. Ghost attachment causes many diseases, such as epilepsy, depression, schizophrenia, and somatic symptom disorders. With the help of master spirits, these conditions can be rapidly improved. For this we created **Woos Spirit Medicine**.</v>
+        <v>A living person is composed of both the physical body and the **spirit** (the living **spirit**). After death, that **spirit** becomes **spirit (ghost)**. For the billions of **spirits (ghosts)**, the only means of survival is to obtain energy by attaching to human beings. Attachment by **spirits (ghosts)** causes many diseases, such as epilepsy, depression, schizophrenia, and somatic symptom disorders. With the help of master spirits, these conditions can be rapidly improved. For this we created **Woos Spirit Medicine**.</v>
       </c>
       <c r="E9" t="str">
         <v>人活着时是由肉体和灵体组成的，死后灵体成为了鬼魂（spirit ghost），但是数以几十亿的鬼魂生存的唯一手段是通过附体人类获得能量。鬼魂附体导致了很多疾病，例如：癫痫、抑郁、精分、躯体化障碍。在高级控制灵的帮助下，这些病症可以迅速被改善。为此我们创建了**吴氏灵魂医学**。</v>
@@ -690,7 +690,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D13" t="str">
-        <v>The Spirit Realm has governors — tremendous master spirits (master spirit), upgraded from ordinary spirit ghosts through the **Universal Matrix of Meta Awareness**.</v>
+        <v>The Spirit Realm has governors — tremendous master spirits (master spirit), upgraded from ordinary **spirits (ghosts)** through the **Universal Matrix of Meta Awareness**.</v>
       </c>
       <c r="E13" t="str">
         <v>灵魂世界有统御者，他们是数量多的高级控制灵（master spirit），是被**万有元神母体**从普通鬼魂中挑选并升级而来</v>
@@ -758,9 +758,8 @@
       <c r="C16" t="str">
         <v>heading</v>
       </c>
-      <c r="D16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Storyline
-----Our story has 2 main stages</v>
+      <c r="D16" t="str">
+        <v>Two Major Chapters</v>
       </c>
       <c r="E16" t="str" xml:space="preserve">
         <v xml:space="preserve">故事线
@@ -876,7 +875,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D21" t="str">
-        <v>We fought only for self-rescue — trying and researching every possible method to kill them. In the process of harming and destroying them, we learned the matter properties, physiological and physical properties of ghost bodies, and communicated through epileptic discharge, auditory hallucination sounds, consciousness dialogue, consciousness control, and other modes — building a verified picture of the spirit world.</v>
+        <v>We fought only for self-rescue — trying and researching every possible method to kill them. In the process of harming and destroying them, we learned the matter properties, physiological and physical properties of **spirits (ghosts)**, and communicated through epileptic discharge, auditory hallucination sounds, consciousness dialogue, consciousness control, and other modes — building a verified picture of the spirit world.</v>
       </c>
       <c r="E21" t="str">
         <v>我们只是为了自救而努力尝试和研究用各种方法去杀死他们。在杀死杀伤他们的过程中我们了解了鬼魂身体的物质，生理属性和物理属性，并且在这个过程中，我们与鬼魂使用癫痫放电、幻听、意识对话、意识控制等各种方式进行交流，了解了灵魂世界大量的真实信息。</v>
@@ -922,7 +921,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D23" t="str">
-        <v>Our greatest regret in Phase A is that we did not engage with attached spirits on other people outside our family, or those in other countries.</v>
+        <v>Our greatest regret in Phase A is that we did not engage with **spirits (ghosts)** on other people outside our family, or those in other countries.</v>
       </c>
       <c r="E23" t="str">
         <v>这个阶段最大的遗憾是，我们没有与外界其他人和其他国家的附体鬼魂进行交流。</v>
@@ -991,7 +990,7 @@
         <v>label</v>
       </c>
       <c r="D26" t="str">
-        <v>A 1 stage</v>
+        <v>A 1</v>
       </c>
       <c r="E26" t="str">
         <v>故事线A 1阶段</v>
@@ -1060,7 +1059,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D29" t="str">
-        <v>During this period, the C1 spirit ghost in my body used the way of releasing high voltage electrostatic in drinks and wine to change the taste of drinks, aimed to fabricate a series of scientific phenomena and laws, which would finally lead to the proof of the existence of Buddhism. The details are complicated to explain clearly in words.</v>
+        <v>During this period, the C1 **spirit (ghost)** in my body used the way of releasing high voltage electrostatic in drinks and wine to change the taste of drinks, aimed to fabricate a series of scientific phenomena and laws, which would finally lead to the proof of the existence of Buddhism. The details are complicated to explain clearly in words.</v>
       </c>
       <c r="E29" t="str">
         <v>在此期间，我体内的C1级别鬼魂通过在饮料和酒中释放高压静电的方式改变饮料口感，目的是伪造一系列科学现象和规律，最终导向佛教存在的"证明"。详情过于复杂，难以用文字完全说清楚。</v>
@@ -1175,7 +1174,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D34" t="str">
-        <v>During this period, Hui 'an, a C1-level ghost in my body, used the way of epileptic seizures to disguise himself as the three great Buddhists in different periods, and finally let my two sons and I convert to Buddhism under the pretext of conveying the divine will. This is actually a big joke, playing tricks on our family like monkeys, which is also the standard paranoia in schizophrenia. However, in the process of cheating and playing tricks, we also exchanged a lot of philosophical cognition and knowledge with the ghost Huian.</v>
+        <v>During this period, Hui 'an, a C1-level **spirit (ghost)** in my body, used the way of epileptic seizures to disguise himself as the three great Buddhists in different periods, and finally let my two sons and I convert to Buddhism under the pretext of conveying the divine will. This is actually a big joke, playing tricks on our family like monkeys, which is also the standard paranoia in schizophrenia. However, in the process of cheating and playing tricks, we also exchanged a lot of philosophical cognition and knowledge with the **spirit (ghost)** Huian.</v>
       </c>
       <c r="E34" t="str">
         <v>在此期间，我体内的C1级别鬼魂使用癫痫发作的方式，分时段伪装成佛教三大菩萨，假借传达神旨，最终让我和两个儿子皈依了佛教。这其实是一个大笑话，把我们全家当像猴子一样耍弄，这也是精神分裂症中标准的妄想症。然而，在欺骗和耍弄过程中，我们与鬼魂惠安也交流了大量的哲学认知与知识。</v>
@@ -1267,7 +1266,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D38" t="str">
-        <v>At Nov 15, 2020, the real identities of spirit ghosts inside us and their tricks were finally debunked. In great fear and anger, we want to exorcise them. After many failures using traditional ways, we recalled that they always forbade us to touch any strong magnets with various excuses in previous communications. So we started using magnets to hurt them.</v>
+        <v>At Nov 15, 2020, the real identities of **spirits (ghosts)** inside us and their tricks were finally debunked. In great fear and anger, we want to exorcise them. After many failures using traditional ways, we recalled that they always forbade us to touch any strong magnets with various excuses in previous communications. So we started using magnets to hurt them.</v>
       </c>
       <c r="E38" t="str">
         <v>2020年11月15日，我们体内鬼魂的真实身份及其把戏终于被揭穿。在极度恐惧和愤怒中，我们想要驱逐它们。在多次尝试传统方法失败后，我们回想起它们在之前交流中总是以各种借口禁止我们接触强磁铁。于是我们开始使用磁铁来伤害它们。</v>
@@ -1290,7 +1289,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D39" t="str">
-        <v>A few days later, the spirit ghost inside my elder son couldn't stand it and left first. Then after a month and a half, the spirit ghost inside my younger son also left due to the same reason. But the spirit ghost in my body was unable to leave even it was already slightly injured, it made me puzzled.</v>
+        <v>A few days later, the **spirit (ghost)** inside my elder son couldn't stand it and left first. Then after a month and a half, the **spirit (ghost)** inside my younger son also left due to the same reason. But the **spirit (ghost)** in my body was unable to leave even it was already slightly injured, it made me puzzled.</v>
       </c>
       <c r="E39" t="str">
         <v>几天后，我大儿子体内的鬼魂首先忍受不了而离开。大约一个半月后，我小儿子体内的鬼魂也因同样的原因离开了。但我体内的鬼魂即使已经受轻伤也无法离开，这让我困惑不解。</v>
@@ -1313,7 +1312,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D40" t="str">
-        <v>I found out that using a strong electrostatic field could greatly weaken it from discharging, and my epilepsy was eliminated immediately once it happens. But the spirit ghost was still inside me and continued played hide and seek with me.</v>
+        <v>I found out that using a strong electrostatic field could greatly weaken it from discharging, and my epilepsy was eliminated immediately once it happens. But the **spirit (ghost)** was still inside me and continued played hide and seek with me.</v>
       </c>
       <c r="E40" t="str">
         <v>我发现使用强静电场可以大幅削弱它的放电能力，而我的癫痫在这种情况发生时会立即消除。但鬼魂仍然在我体内，继续与我捉迷藏。</v>
@@ -1405,7 +1404,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D44" t="str">
-        <v>During this stage, several ways of interfering, hurting and killing C1 spirit ghost were found and confirmed.</v>
+        <v>During this stage, several ways of interfering, hurting and killing C1 **spirit (ghost)** were found and confirmed.</v>
       </c>
       <c r="E44" t="str">
         <v>在这个阶段，找到并确认了几种干扰、伤害和杀死C1级别鬼魂的方法。</v>
@@ -1428,7 +1427,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D45" t="str">
-        <v>The limitation of magnet therapy aroused the interest of an advanced spirit (not a master spirit) who died in China about 1500 years ago. It quietly participated in the process of exploring how to expel and kill the C1-level spirit ghost Huian. In this process, it used the way of consciousness transmission to give me hints and inspiration, and also manipulated the behavior of Hui 'an, and finally let me know how to kill and expel huian accurately and efficiently.</v>
+        <v>The limitation of magnet therapy aroused the interest of an advanced spirit (not a master spirit) who died in China about 1500 years ago. It quietly participated in the process of exploring how to expel and kill the C1-level **spirit (ghost)** Huian. In this process, it used the way of consciousness transmission to give me hints and inspiration, and also manipulated the behavior of Hui 'an, and finally let me know how to kill and expel huian accurately and efficiently.</v>
       </c>
       <c r="E45" t="str">
         <v>磁铁疗法的局限性引起了一位在中国去世约1500年的高级灵（不是高级控制灵）的兴趣。它悄悄参与了探索如何驱逐和杀死C1级别鬼魂惠安的过程。在此过程中，它使用意识传输的方式给我提示和灵感，同时也操控C1级别鬼魂惠安的行为，最终让我知道了如何精确高效地杀死和驱逐C1级别鬼魂</v>
@@ -1451,7 +1450,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D46" t="str">
-        <v>As a father, I pester, fight and coexist with Hui 'an every day, forming a subtle relationship that is both enemy and friend. In the process of hurting ghosts, we also exchanged a lot of knowledge about spirit-related information. Finally, the advanced spirit appeared and demonstrated extraordinary ability. It explained various puzzles from the past year and taught me more about the spiritual realm, then left my body and vanished quickly.</v>
+        <v>As a father, I pester, fight and coexist with Hui 'an every day, forming a subtle relationship that is both enemy and friend. In the process of hurting **spirits (ghosts)**, we also exchanged a lot of knowledge about spirit-related information. Finally, the advanced spirit appeared and demonstrated extraordinary ability. It explained various puzzles from the past year and taught me more about the spiritual realm, then left my body and vanished quickly.</v>
       </c>
       <c r="E46" t="str">
         <v>做父亲的我每天与C1级别鬼魂惠安纠缠、搏斗、共存，形成了一种既是敌人又是朋友的微妙关系。在伤害鬼魂的过程中，我们也交流了大量关于灵魂相关信息的知识。最终，这个高级领现身并展示了其非凡能力。它解释了过去一年中的各种困惑，并教了我更多灵魂世界的知识，然后它离开了我的身体并迅速消失</v>
@@ -1543,7 +1542,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D50" t="str">
-        <v>In December 2023, as a father, I was once again attached by a C2-level ghost, Qing Xiaoxian. During its 1,700 years as a ghost, it swallowed about 5,000 to 10,000 other spirits, thus forming a very large body. It turned our house into a haunted house and created multiple Remote Port Organs (RPO) attached to both sons; the main body could communicate with them remotely.</v>
+        <v>In December 2023, as a father, I was once again attached by a C2-level **spirit (ghost)**, Qing Xiaoxian. During its 1,700 years as a **spirit (ghost)**, it swallowed about 5,000 to 10,000 other **spirits (ghosts)**, thus forming a very large body. It turned our house into a haunted house and created multiple Remote Port Organs (RPO) attached to both sons; the main body could communicate with them remotely.</v>
       </c>
       <c r="E50" t="str">
         <v>2023年12月，作为父亲的我又被一个C2级别的鬼魂青小仙再次附体。在它作为鬼魂存在的1700年间，吞噬了大约5000到10000个其他鬼魂，从而拥有了一个十分庞大的躯体。它将吴氏家变成了一座鬼屋，并制造出多个分身（RPO）附身于两个儿子身上，其身体主体能够与这些分身进行远程交流</v>
@@ -1566,7 +1565,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D51" t="str">
-        <v>In my body, this ghost has caused many manifestations such as schizophrenia, bipolar disorder, epilepsy and somatization. It also attacked my heart with extremely powerful current, and had symptoms of acute heart failure. In two sons, it caused chronic fatigue, depression, pain disorder and irritable bowel syndrome, as well as other somatization symptoms</v>
+        <v>In my body, this **spirit (ghost)** has caused many manifestations such as schizophrenia, bipolar disorder, epilepsy and somatization. It also attacked my heart with extremely powerful current, and had symptoms of acute heart failure. In two sons, it caused chronic fatigue, depression, pain disorder and irritable bowel syndrome, as well as other somatization symptoms.</v>
       </c>
       <c r="E51" t="str">
         <v>在我身上，这个鬼魂引发了精神分裂症、躁郁症、癫痫和躯体化症状等多种表现。它还用极其强大的电流攻击过我的心脏，出现过急性心衰的症状。在两个儿子身上，它导致了慢性疲劳、抑郁、疼痛障碍和肠易激综合征，以及其他躯体化症状</v>
@@ -1589,7 +1588,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D52" t="str">
-        <v>We continued to refine exorcism and ghost-elimination techniques and ultimately successfully destroyed this ghost.</v>
+        <v>We continued to refine exorcism and **spirit (ghost)** elimination techniques and ultimately successfully destroyed this **spirit (ghost)**.</v>
       </c>
       <c r="E52" t="str">
         <v>我们继续完善驱鬼和杀鬼技术，最终成功地消灭了这个鬼魂。</v>
@@ -1612,7 +1611,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D53" t="str">
-        <v>From September 2024 to January 2025, as a father, I was again attached by a C3-level ghost, Qian Kai. Qian Kai's density was far higher than the C2-level Qing Xiaoxian. The higher a ghost's density, the stronger its ability—so Qian Kai's thought-control and pathogenic power were stronger as well. We continued self-rescue and eliminated this ghost.</v>
+        <v>From September 2024 to January 2025, as a father, I was again attached by a C3-level **spirit (ghost)**, Qian Kai. Qian Kai's density was far higher than the C2-level Qing Xiaoxian. The higher a **spirit (ghost)**'s density, the stronger its ability—so Qian Kai's thought-control and pathogenic power were stronger as well. We continued self-rescue and eliminated this **spirit (ghost)**.</v>
       </c>
       <c r="E53" t="str">
         <v>*2024年9月到2025年1月，做父亲的我再次被一个C3级别的鬼魂钱凯附体。钱凯的身体密度要远高于C2级别的青小仙。鬼魂的身体密度越高能力越强。因此，钱凯的思维控制和致病能力也越强。我们同样继续自救，杀死了这个鬼魂</v>
@@ -1681,7 +1680,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D56" t="str">
-        <v>In this phase, Caros Woo communicated with a large number of attached ghosts in North America through TikTok live streams, completely confirming all the spirit world truths we obtained in Phase A. With the help of master spirits, Caros Woo obtained the superpower to remotely control attached ghosts in North America. This superpower is the foundation upon which we built ASRA.</v>
+        <v>In this phase, Caros Woo communicated with a large number of attached **spirits (ghosts)** in North America through TikTok live streams, completely confirming all the spirit world truths we obtained in Phase A. With the help of master spirits, Caros Woo obtained the superpower to remotely control attached **spirits (ghosts)** in North America. This superpower is the foundation upon which we built ASRA.</v>
       </c>
       <c r="E56" t="str">
         <v>在这个阶段，Caros Woo通过TikTok直播间与北美的大量附体鬼魂进行了交流，完全证实了A阶段我们获得的所有灵魂世界真相。并且在高级控制灵的帮助下，Caros Woo获得了远程控制北美附体鬼魂的超能力。这种超能力正是我们建设ASRA的基础。</v>
@@ -1773,7 +1772,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D60" t="str">
-        <v>A great number of master spirits and hybrid spirits reached out to us as father and sons, letting us know that the spirit world surprisingly has administrators and creators. Master spirits gave us a great deal of help. Caros Woo obtained the PRCASG superpower to remotely control attached spirits in North America, so that while in China he could remotely control spirits on the other side of the globe. This PRCASG superpower is the basis on which we built ASRA.</v>
+        <v>A great number of master spirits and hybrid spirits reached out to us as father and sons, letting us know that the spirit world surprisingly has administrators and creators. Master spirits gave us a great deal of help. Caros Woo obtained the PRCASG superpower to remotely control attached **spirits (ghosts)** in North America, so that while in China he could remotely control **spirits (ghosts)** on the other side of the globe. This PRCASG superpower is the basis on which we built ASRA.</v>
       </c>
       <c r="E60" t="str">
         <v>大量高级控制灵（master spirit）以及混合控制灵（hybrid spirit）与我们父子联系，让我们知道灵魂世界竟然有管理者和造物主。高级控制灵给我们很多帮助，Caros Woo获得了远程控制北美附体鬼魂的PRCASG超能力，让Caros Woo在中国就可以直接远程控制远在地球另一端北美的附体鬼魂。这种PRCASG超能力正是我们建设ASRA的基础</v>
@@ -1819,7 +1818,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D62" t="str">
-        <v>Most importantly, we were told: every attached ghost on us during Phase A was deliberately arranged by master spirits. The killing of those attached ghosts was permitted as research material. All the suffering, deception, and taunting storylines were also part of their plan — to let us understand their operating style and character disposition.</v>
+        <v>Most importantly, we were told: every attached **spirit (ghost)** on us during Phase A was deliberately arranged by master spirits. The killing of those attached **spirits (ghosts)** was permitted as research material. All the suffering, deception, and taunting storylines were also part of their plan — to let us understand their operating style and character disposition.</v>
       </c>
       <c r="E62" t="str">
         <v>最重要的是，我们被告知，A阶段在我们身上附体的鬼魂都是被高级控制灵（master spirit）刻意安排进来的。这些附体鬼魂被杀死是被许可作为研究使用的。所有的病痛折磨、欺骗、戏弄性的故事也是他们计划的一部分，让我们了解到了他们的做事风格以及性格秉性。</v>
@@ -1888,7 +1887,7 @@
         <v>heading</v>
       </c>
       <c r="D65" t="str">
-        <v>Spirit Medicine and video archives</v>
+        <v>Woos Spirit Medicine and video archives</v>
       </c>
       <c r="E65" t="str">
         <v>吴氏灵魂医学与视频档案</v>
@@ -1911,7 +1910,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D66" t="str">
-        <v>During this period, Spirit Medicine was formally established. Part of the **Woos Spirit Medicine** and **Universal Matrix of Meta Awareness** video archive series were filmed.</v>
+        <v>During this period, **Woos Spirit Medicine** was formally established. Part of the **Woos Spirit Medicine** and **Universal Matrix of Meta Awareness** video archive series were filmed.</v>
       </c>
       <c r="E66" t="str">
         <v>在此期间，正式创建了**吴氏灵魂医学**。拍摄了**吴氏灵魂医学**和**万有元神母体**系列视频档案中的一部分视频。</v>
@@ -2210,7 +2209,7 @@
         <v>label</v>
       </c>
       <c r="D79" t="str">
-        <v>Feb 2025 -- Mar 2026</v>
+        <v>February 2025 — March 2026</v>
       </c>
       <c r="E79" t="str">
         <v>2025年2月—2026年3月</v>
@@ -2233,7 +2232,7 @@
         <v>label</v>
       </c>
       <c r="D80" t="str">
-        <v>PhaseB . Tiktok livestream &amp; the born of Spirit medicine</v>
+        <v>Phase B — TikTok livestreams &amp; Woos Spirit Medicine</v>
       </c>
       <c r="E80" t="str">
         <v>B阶段 · TikTok 直播与**吴氏灵魂医学**档案</v>

--- a/docs/page-copy/03-创始人故事.xlsx
+++ b/docs/page-copy/03-创始人故事.xlsx
@@ -529,7 +529,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D6" t="str">
-        <v>I, John LONG WOO, and my two sons Caros Woo and Sam, the three of us, have too many legendary stories with the spiritual realm. These experiences make us the first door opener in the spiritual realm and the first explorer of the truth of **spirit (soul)** life.</v>
+        <v xml:space="preserve">I, John LONG WOO, and my two sons Caros Woo and Sam, the three of us, have too many legendary stories with the spiritual realm. These experiences make us the first door opener in the spiritual realm and the first explorer of the truth of **spirit** </v>
       </c>
       <c r="E6" t="str">
         <v>我， John LONG WOO, 和我的两个儿子Caros Woo和Sam，我们父子三人，与灵魂世界有太多传奇的故事。这些经历造就我们是灵魂世界首位开门者，并且是灵魂生命真相的首位探索者。</v>
@@ -598,7 +598,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D9" t="str">
-        <v>A living person is composed of both the physical body and the **spirit** (the living **spirit**). After death, that **spirit** becomes **spirit (ghost)**. For the billions of **spirits (ghosts)**, the only means of survival is to obtain energy by attaching to human beings. Attachment by **spirits (ghosts)** causes many diseases, such as epilepsy, depression, schizophrenia, and somatic symptom disorders. With the help of master spirits, these conditions can be rapidly improved. For this we created **Woos Spirit Medicine**.</v>
+        <v>A living person is composed of both the physical body and the **spirit (soul)**. After death, that **spirit(soul) ** becomes **spirit (ghost)**. For the billions of **spirits (ghosts)**, the only means of survival is to obtain energy by attaching to human beings. Attachment by **spirits (ghosts)** causes many diseases, such as epilepsy, depression, schizophrenia, and somatic symptom disorders. With the help of master spirits, these conditions can be rapidly improved. For this we created **Woos Spirit Medicine**.</v>
       </c>
       <c r="E9" t="str">
         <v>人活着时是由肉体和灵体组成的，死后灵体成为了鬼魂（spirit ghost），但是数以几十亿的鬼魂生存的唯一手段是通过附体人类获得能量。鬼魂附体导致了很多疾病，例如：癫痫、抑郁、精分、躯体化障碍。在高级控制灵的帮助下，这些病症可以迅速被改善。为此我们创建了**吴氏灵魂医学**。</v>

--- a/docs/page-copy/03-创始人故事.xlsx
+++ b/docs/page-copy/03-创始人故事.xlsx
@@ -440,7 +440,7 @@
         <v>John Long Woo · Caros Woo · Sam</v>
       </c>
       <c r="E2" t="str">
-        <v>John Long Woo· Caros Woo · Sam</v>
+        <v>John Long Woo· Caros Woo · Sam Woo</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -529,7 +529,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D6" t="str">
-        <v xml:space="preserve">I, John LONG WOO, and my two sons Caros Woo and Sam, the three of us, have too many legendary stories with the spiritual realm. These experiences make us the first door opener in the spiritual realm and the first explorer of the truth of **spirit** </v>
+        <v xml:space="preserve">I, John LONG WOO, and my two sons Caros Woo and Sam Woo, the three of us, have too many legendary stories with the spiritual realm. These experiences make us the first door opener to the spiritual realm and the first explorer of the truth of **spirit** </v>
       </c>
       <c r="E6" t="str">
         <v>我， John LONG WOO, 和我的两个儿子Caros Woo和Sam，我们父子三人，与灵魂世界有太多传奇的故事。这些经历造就我们是灵魂世界首位开门者，并且是灵魂生命真相的首位探索者。</v>
@@ -690,7 +690,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D13" t="str">
-        <v>The Spirit Realm has governors — tremendous master spirits (master spirit), upgraded from ordinary **spirits (ghosts)** through the **Universal Matrix of Meta Awareness**.</v>
+        <v>The Spirit Realm has governors — tremendous master spirits, upgraded from ordinary **spirits (ghosts)** through the **Universal Matrix of Meta Awareness**.</v>
       </c>
       <c r="E13" t="str">
         <v>灵魂世界有统御者，他们是数量多的高级控制灵（master spirit），是被**万有元神母体**从普通鬼魂中挑选并升级而来</v>
@@ -783,7 +783,7 @@
         <v>heading</v>
       </c>
       <c r="D17" t="str">
-        <v>Phase A — May 2014 through February 2025</v>
+        <v>Phase A — May 2014 - February 2025</v>
       </c>
       <c r="E17" t="str">
         <v>A阶段：2014年5月至2025年2月</v>
@@ -1174,7 +1174,7 @@
         <v>paragraph / other</v>
       </c>
       <c r="D34" t="str">
-        <v>During this period, Hui 'an, a C1-level **spirit (ghost)** in my body, used the way of epileptic seizures to disguise himself as the three great Buddhists in different periods, and finally let my two sons and I convert to Buddhism under the pretext of conveying the divine will. This is actually a big joke, playing tricks on our family like monkeys, which is also the standard paranoia in schizophrenia. However, in the process of cheating and playing tricks, we also exchanged a lot of philosophical cognition and knowledge with the **spirit (ghost)** Huian.</v>
+        <v>During this period, Hui 'an, a C1-level **spirit (ghost)** in my body, used the way of epileptic seizures to disguise itself as the three great Buddhists in different periods, and finally let my two sons and I convert to Buddhism under the pretext of conveying the divine will. This is actually a big joke, playing tricks on our family like monkeys, which is also the standard paranoia in schizophrenia. However, in the process of cheating and playing tricks, we also exchanged a lot of philosophical cognition and knowledge with the **spirit (ghost)** Huian.</v>
       </c>
       <c r="E34" t="str">
         <v>在此期间，我体内的C1级别鬼魂使用癫痫发作的方式，分时段伪装成佛教三大菩萨，假借传达神旨，最终让我和两个儿子皈依了佛教。这其实是一个大笑话，把我们全家当像猴子一样耍弄，这也是精神分裂症中标准的妄想症。然而，在欺骗和耍弄过程中，我们与鬼魂惠安也交流了大量的哲学认知与知识。</v>
@@ -1634,7 +1634,7 @@
         <v>heading</v>
       </c>
       <c r="D54" t="str">
-        <v>Phase B — February 2025 through March 2026</v>
+        <v>Phase B — February 2025 - March 2026</v>
       </c>
       <c r="E54" t="str">
         <v>B阶段：2025年2月至2026年3月</v>
